--- a/output/2026-09-03/enriched_analysis.xlsx
+++ b/output/2026-09-03/enriched_analysis.xlsx
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1609,27 +1609,27 @@
         <v>109.51</v>
       </c>
       <c r="J12" t="n">
-        <v>91.62</v>
+        <v>91.7</v>
       </c>
       <c r="K12" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="L12" t="n">
         <v>70.88</v>
       </c>
       <c r="M12" t="n">
-        <v>8.390000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.298</v>
+        <v>0.302</v>
       </c>
       <c r="Q12" t="n">
         <v>2815</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ganesh Consumer Products Limited</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5477,23 +5477,23 @@
         <v>109.51</v>
       </c>
       <c r="D12" t="n">
-        <v>91.62</v>
+        <v>91.7</v>
       </c>
       <c r="E12" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="F12" t="n">
         <v>70.88</v>
       </c>
       <c r="G12" t="n">
-        <v>8.390000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ganesh Consumer Products Limited</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">

--- a/output/2026-09-03/enriched_analysis.xlsx
+++ b/output/2026-09-03/enriched_analysis.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="Q2" t="n">
-        <v>2615</v>
+        <v>2591</v>
       </c>
       <c r="R2" t="n">
-        <v>8.99</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.408</v>
+        <v>0.396</v>
       </c>
       <c r="Q3" t="n">
-        <v>966</v>
+        <v>995</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>28.4</v>
       </c>
       <c r="S3" t="n">
         <v>19</v>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="Q4" t="n">
-        <v>1273</v>
+        <v>1330</v>
       </c>
       <c r="R4" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="S4" t="n">
         <v>55</v>
@@ -1054,10 +1054,10 @@
         <v>0.044</v>
       </c>
       <c r="Q6" t="n">
-        <v>16458</v>
+        <v>16565</v>
       </c>
       <c r="R6" t="n">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="S6" t="n">
         <v>83</v>
@@ -1151,7 +1151,7 @@
         <v>0.049</v>
       </c>
       <c r="Q7" t="n">
-        <v>15811</v>
+        <v>15755</v>
       </c>
       <c r="R7" t="n">
         <v>20</v>
@@ -1248,7 +1248,7 @@
         <v>0.006</v>
       </c>
       <c r="Q8" t="n">
-        <v>4097</v>
+        <v>4136</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.163</v>
+        <v>0.159</v>
       </c>
       <c r="Q9" t="n">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="R9" t="n">
-        <v>56.8</v>
+        <v>58.5</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.49</v>
+        <v>0.496</v>
       </c>
       <c r="Q10" t="n">
-        <v>1636</v>
+        <v>1616</v>
       </c>
       <c r="R10" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="S10" t="n">
         <v>581</v>
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="Q11" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="R11" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="S11" t="n">
         <v>-8</v>
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.302</v>
+        <v>0.294</v>
       </c>
       <c r="Q12" t="n">
-        <v>2815</v>
+        <v>2885</v>
       </c>
       <c r="R12" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.544</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="R13" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="S13" t="n">
         <v>22</v>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.647</v>
+        <v>0.649</v>
       </c>
       <c r="Q14" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="R14" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="S14" t="n">
         <v>21</v>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="Q15" t="n">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="R15" t="n">
-        <v>6.13</v>
+        <v>6.03</v>
       </c>
       <c r="S15" t="n">
         <v>118</v>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.09</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>880</v>
+        <v>916</v>
       </c>
       <c r="R16" t="n">
-        <v>8.65</v>
+        <v>9.02</v>
       </c>
       <c r="S16" t="n">
         <v>7</v>
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.204</v>
+        <v>0.192</v>
       </c>
       <c r="Q17" t="n">
-        <v>1472</v>
+        <v>1570</v>
       </c>
       <c r="R17" t="n">
-        <v>51.4</v>
+        <v>54.8</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
@@ -2210,10 +2210,10 @@
         <v>0.007</v>
       </c>
       <c r="Q18" t="n">
-        <v>5703</v>
+        <v>5832</v>
       </c>
       <c r="R18" t="n">
-        <v>9.640000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="S18" t="n">
         <v>43</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.539</v>
+        <v>0.544</v>
       </c>
       <c r="Q19" t="n">
-        <v>1120</v>
+        <v>1111</v>
       </c>
       <c r="R19" t="n">
-        <v>57</v>
+        <v>56.6</v>
       </c>
       <c r="S19" t="n">
         <v>21</v>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.363</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>2775</v>
+        <v>2756</v>
       </c>
       <c r="R20" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="S20" t="n">
         <v>6</v>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="Q21" t="n">
-        <v>859</v>
+        <v>877</v>
       </c>
       <c r="R21" t="n">
-        <v>91.8</v>
+        <v>93.7</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2575,19 +2575,19 @@
         <v>27.97</v>
       </c>
       <c r="J22" t="n">
-        <v>29.14</v>
+        <v>29.42</v>
       </c>
       <c r="K22" t="n">
-        <v>-4</v>
+        <v>-4.9</v>
       </c>
       <c r="L22" t="n">
         <v>69.03</v>
       </c>
       <c r="M22" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.241</v>
+        <v>1.099</v>
       </c>
       <c r="Q22" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="R22" t="n">
-        <v>78</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="S22" t="n">
         <v>-1</v>
@@ -2695,10 +2695,10 @@
         <v>0.001</v>
       </c>
       <c r="Q23" t="n">
-        <v>358094</v>
+        <v>353835</v>
       </c>
       <c r="R23" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="S23" t="n">
         <v>7</v>
@@ -2792,10 +2792,10 @@
         <v>0.052</v>
       </c>
       <c r="Q24" t="n">
-        <v>5028</v>
+        <v>5044</v>
       </c>
       <c r="R24" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="S24" t="n">
         <v>-25</v>
@@ -2889,10 +2889,10 @@
         <v>0.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>2156</v>
+        <v>2139</v>
       </c>
       <c r="R25" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.968</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>5002</v>
+        <v>5139</v>
       </c>
       <c r="R26" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="Q27" t="n">
-        <v>3248</v>
+        <v>3267</v>
       </c>
       <c r="R27" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="S27" t="n">
         <v>17</v>
@@ -3177,13 +3177,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.4</v>
+        <v>0.387</v>
       </c>
       <c r="Q28" t="n">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="R28" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="S28" t="n">
         <v>246</v>
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.271</v>
+        <v>0.272</v>
       </c>
       <c r="Q29" t="n">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="R29" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="S29" t="n">
         <v>12</v>
@@ -3371,13 +3371,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="Q30" t="n">
-        <v>776</v>
+        <v>786</v>
       </c>
       <c r="R30" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="S30" t="n">
         <v>185</v>
@@ -3446,33 +3446,33 @@
         <v>13.12</v>
       </c>
       <c r="J31" t="n">
-        <v>12.41</v>
+        <v>12.44</v>
       </c>
       <c r="K31" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L31" t="n">
         <v>69.12</v>
       </c>
       <c r="M31" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="N31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.398</v>
+        <v>0.419</v>
       </c>
       <c r="Q31" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="R31" t="n">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="S31" t="n">
         <v>-61</v>
@@ -3539,33 +3539,33 @@
         <v>168.82</v>
       </c>
       <c r="J32" t="n">
-        <v>201.21</v>
+        <v>199.75</v>
       </c>
       <c r="K32" t="n">
-        <v>-16.1</v>
+        <v>-15.5</v>
       </c>
       <c r="L32" t="n">
         <v>64.08</v>
       </c>
       <c r="M32" t="n">
-        <v>8.07</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.182</v>
+        <v>1.203</v>
       </c>
       <c r="Q32" t="n">
-        <v>683</v>
+        <v>696</v>
       </c>
       <c r="R32" t="n">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="S32" t="n">
         <v>-1</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="Q33" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.298</v>
+        <v>0.294</v>
       </c>
       <c r="Q34" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R34" t="n">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="S34" t="n">
         <v>21</v>
@@ -3848,13 +3848,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="Q35" t="n">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="R35" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="S35" t="n">
         <v>61</v>
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.325</v>
+        <v>0.316</v>
       </c>
       <c r="Q36" t="n">
-        <v>2268</v>
+        <v>2332</v>
       </c>
       <c r="R36" t="n">
-        <v>19.5</v>
+        <v>20.1</v>
       </c>
       <c r="S36" t="n">
         <v>18</v>
@@ -4040,13 +4040,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="Q37" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="R37" t="n">
-        <v>24.1</v>
+        <v>25</v>
       </c>
       <c r="S37" t="n">
         <v>12</v>
@@ -4137,13 +4137,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.279</v>
+        <v>0.277</v>
       </c>
       <c r="Q38" t="n">
-        <v>3658</v>
+        <v>3683</v>
       </c>
       <c r="R38" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4332,10 +4332,10 @@
         <v>0.099</v>
       </c>
       <c r="Q40" t="n">
-        <v>1500</v>
+        <v>1493</v>
       </c>
       <c r="R40" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="S40" t="n">
         <v>6</v>
@@ -4429,7 +4429,7 @@
         <v>0.188</v>
       </c>
       <c r="Q41" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="R41" t="n">
         <v>12</v>
@@ -4526,7 +4526,7 @@
         <v>0.611</v>
       </c>
       <c r="Q42" t="n">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="R42" t="n">
         <v>32.1</v>
@@ -4568,16 +4568,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -4597,84 +4597,84 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>171.55</v>
+        <v>275.45</v>
       </c>
       <c r="J43" t="n">
-        <v>173.91</v>
+        <v>292.28</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.4</v>
+        <v>-5.8</v>
       </c>
       <c r="L43" t="n">
-        <v>65.64</v>
+        <v>70.45</v>
       </c>
       <c r="M43" t="n">
-        <v>2.61</v>
+        <v>1.29</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.137</v>
+        <v>0.083</v>
       </c>
       <c r="Q43" t="n">
-        <v>1904</v>
+        <v>1548</v>
       </c>
       <c r="R43" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="S43" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="U43" t="n">
         <v>-4</v>
       </c>
       <c r="V43" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="W43" t="n">
-        <v>14.2</v>
+        <v>19.9</v>
       </c>
       <c r="X43" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="Y43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
-        <v>183.14</v>
+        <v>295.62</v>
       </c>
       <c r="AB43" t="n">
-        <v>189.81</v>
+        <v>321.01</v>
       </c>
       <c r="AC43" t="n">
-        <v>-16.9</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -4694,69 +4694,69 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>275.45</v>
+        <v>171.55</v>
       </c>
       <c r="J44" t="n">
-        <v>292.28</v>
+        <v>175.08</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.8</v>
+        <v>-2</v>
       </c>
       <c r="L44" t="n">
-        <v>70.45</v>
+        <v>65.64</v>
       </c>
       <c r="M44" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="P44" t="n">
         <v>0.082</v>
       </c>
       <c r="Q44" t="n">
-        <v>1572</v>
+        <v>1922</v>
       </c>
       <c r="R44" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>-3</v>
       </c>
       <c r="T44" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="U44" t="n">
         <v>-4</v>
       </c>
       <c r="V44" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="W44" t="n">
-        <v>19.9</v>
+        <v>14.2</v>
       </c>
       <c r="X44" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="Y44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AA44" t="n">
-        <v>295.62</v>
+        <v>183.14</v>
       </c>
       <c r="AB44" t="n">
-        <v>321.01</v>
+        <v>189.81</v>
       </c>
       <c r="AC44" t="n">
-        <v>-7.4</v>
+        <v>-16.9</v>
       </c>
     </row>
     <row r="45">
@@ -4814,13 +4814,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.283</v>
+        <v>0.286</v>
       </c>
       <c r="Q45" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="R45" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="S45" t="n">
         <v>16</v>
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="Q46" t="n">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="R46" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
@@ -5001,7 +5001,7 @@
         <v>0.074</v>
       </c>
       <c r="Q47" t="n">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="R47" t="n">
         <v>23.2</v>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5827,19 +5827,19 @@
         <v>27.97</v>
       </c>
       <c r="D22" t="n">
-        <v>29.14</v>
+        <v>29.42</v>
       </c>
       <c r="E22" t="n">
-        <v>-4</v>
+        <v>-4.9</v>
       </c>
       <c r="F22" t="n">
         <v>69.03</v>
       </c>
       <c r="G22" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -6142,23 +6142,23 @@
         <v>13.12</v>
       </c>
       <c r="D31" t="n">
-        <v>12.41</v>
+        <v>12.44</v>
       </c>
       <c r="E31" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="F31" t="n">
         <v>69.12</v>
       </c>
       <c r="G31" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="H31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
@@ -6177,23 +6177,23 @@
         <v>168.82</v>
       </c>
       <c r="D32" t="n">
-        <v>201.21</v>
+        <v>199.75</v>
       </c>
       <c r="E32" t="n">
-        <v>-16.1</v>
+        <v>-15.5</v>
       </c>
       <c r="F32" t="n">
         <v>64.08</v>
       </c>
       <c r="G32" t="n">
-        <v>8.07</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
@@ -6550,70 +6550,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>171.55</v>
+        <v>275.45</v>
       </c>
       <c r="D43" t="n">
-        <v>173.91</v>
+        <v>292.28</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.4</v>
+        <v>-5.8</v>
       </c>
       <c r="F43" t="n">
-        <v>65.64</v>
+        <v>70.45</v>
       </c>
       <c r="G43" t="n">
-        <v>2.61</v>
+        <v>1.29</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>275.45</v>
+        <v>171.55</v>
       </c>
       <c r="D44" t="n">
-        <v>292.28</v>
+        <v>175.08</v>
       </c>
       <c r="E44" t="n">
-        <v>-5.8</v>
+        <v>-2</v>
       </c>
       <c r="F44" t="n">
-        <v>70.45</v>
+        <v>65.64</v>
       </c>
       <c r="G44" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
     </row>
